--- a/test/fixtures/xlsx/conformance/conformance.xlsx
+++ b/test/fixtures/xlsx/conformance/conformance.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="321">
   <si>
     <t xml:space="preserve">:enum Flag</t>
   </si>
@@ -230,6 +230,15 @@
     <t xml:space="preserve">one field of another table's row</t>
   </si>
   <si>
+    <t xml:space="preserve">owners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Owners[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a row of another table per element</t>
+  </si>
+  <si>
     <t xml:space="preserve">count</t>
   </si>
   <si>
@@ -332,6 +341,9 @@
     <t xml:space="preserve">00000000-0000-0000-0000-000000000000;ffffffff-ffff-ffff-ffff-ffffffffffff</t>
   </si>
   <si>
+    <t xml:space="preserve">2;3</t>
+  </si>
+  <si>
     <t xml:space="preserve">-1</t>
   </si>
   <si>
@@ -365,6 +377,9 @@
     <t xml:space="preserve">None;One;Large</t>
   </si>
   <si>
+    <t xml:space="preserve">1;2;3</t>
+  </si>
+  <si>
     <t xml:space="preserve">east_tower_small_leg_east_tower</t>
   </si>
   <si>
@@ -434,6 +449,9 @@
     <t xml:space="preserve">é</t>
   </si>
   <si>
+    <t xml:space="preserve">2;1</t>
+  </si>
+  <si>
     <t xml:space="preserve">-2</t>
   </si>
   <si>
@@ -485,6 +503,9 @@
     <t xml:space="preserve">-0.5</t>
   </si>
   <si>
+    <t xml:space="preserve">3;1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1002</t>
   </si>
   <si>
@@ -503,6 +524,9 @@
     <t xml:space="preserve">Stat_Attack_Level01</t>
   </si>
   <si>
+    <t xml:space="preserve">1;2;1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1003</t>
   </si>
   <si>
@@ -542,6 +566,9 @@
     <t xml:space="preserve">Stat_Attack_Level02</t>
   </si>
   <si>
+    <t xml:space="preserve">3;2</t>
+  </si>
+  <si>
     <t xml:space="preserve">1006</t>
   </si>
   <si>
@@ -551,6 +578,9 @@
     <t xml:space="preserve">1073741863</t>
   </si>
   <si>
+    <t xml:space="preserve">2;3;1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1007</t>
   </si>
   <si>
@@ -591,6 +621,9 @@
   </si>
   <si>
     <t xml:space="preserve">1073741878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;3;2</t>
   </si>
   <si>
     <t xml:space="preserve">1011</t>
@@ -986,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:AC67"/>
+  <dimension ref="B2:AD67"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1074,10 +1107,13 @@
         <v>72</v>
       </c>
       <c r="AB3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC3" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -1145,12 +1181,15 @@
         <v>70</v>
       </c>
       <c r="AA4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB4" t="s">
         <v>36</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1219,13 +1258,16 @@
         <v>71</v>
       </c>
       <c r="AA5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1301,6 +1343,9 @@
       <c r="AC6" t="s">
         <v>26</v>
       </c>
+      <c r="AD6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
@@ -1328,34 +1373,34 @@
         <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="S7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s">
         <v>6</v>
       </c>
       <c r="U7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y7" t="s">
         <v>7</v>
@@ -1364,60 +1409,63 @@
         <v>7</v>
       </c>
       <c r="AA7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB7" t="s">
         <v>7</v>
       </c>
-      <c r="AB7" t="s">
-        <v>78</v>
-      </c>
       <c r="AC7" t="s">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="J8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T8" t="s">
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="W8" t="s">
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Y8" t="s">
         <v>10</v>
@@ -1429,104 +1477,110 @@
         <v>10</v>
       </c>
       <c r="AB8" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="J9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="R9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="T9" t="s">
         <v>15</v>
       </c>
       <c r="U9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="V9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="X9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Y9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AB9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AC9" t="s">
-        <v>94</v>
+        <v>111</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10">
       <c r="J10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s">
         <v>13</v>
       </c>
       <c r="L10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="R10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="S10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="T10" t="s">
         <v>12</v>
@@ -1535,716 +1589,752 @@
         <v>13</v>
       </c>
       <c r="V10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="W10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="X10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Y10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA10" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AB10" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="AC10" t="s">
-        <v>94</v>
+        <v>122</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11">
       <c r="J11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="M11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="O11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="R11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="S11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="T11" t="s">
         <v>6</v>
       </c>
       <c r="U11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="V11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="W11" t="s">
         <v>12</v>
       </c>
       <c r="X11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="Y11" t="s">
         <v>10</v>
       </c>
       <c r="Z11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AB11" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="AC11" t="s">
-        <v>107</v>
+        <v>134</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="12">
       <c r="J12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="O12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="P12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="R12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="S12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="T12" t="s">
         <v>9</v>
       </c>
       <c r="U12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="W12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="Y12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z12" t="s">
         <v>10</v>
       </c>
       <c r="AA12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AB12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="AC12" t="s">
-        <v>107</v>
+        <v>147</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="J13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T13" t="s">
         <v>9</v>
       </c>
       <c r="U13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y13" t="s">
         <v>10</v>
       </c>
       <c r="Z13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA13" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="AB13" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="AC13" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="14">
       <c r="J14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s">
         <v>150</v>
       </c>
-      <c r="L14" t="s">
-        <v>144</v>
-      </c>
       <c r="M14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O14" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T14" t="s">
         <v>9</v>
       </c>
       <c r="U14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z14" t="s">
         <v>10</v>
       </c>
       <c r="AA14" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="AB14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AC14" t="s">
-        <v>94</v>
+        <v>159</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="J15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="L15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M15" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N15" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O15" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T15" t="s">
         <v>9</v>
       </c>
       <c r="U15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AB15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AC15" t="s">
-        <v>94</v>
+        <v>165</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="J16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K16" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M16" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N16" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O16" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T16" t="s">
         <v>9</v>
       </c>
       <c r="U16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z16" t="s">
         <v>10</v>
       </c>
       <c r="AA16" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AC16" t="s">
-        <v>94</v>
+        <v>172</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17">
       <c r="J17" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="L17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M17" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O17" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="P17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T17" t="s">
         <v>9</v>
       </c>
       <c r="U17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y17" t="s">
         <v>10</v>
       </c>
       <c r="Z17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA17" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AB17" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AC17" t="s">
-        <v>94</v>
+        <v>176</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="18">
       <c r="J18" t="s">
+        <v>177</v>
+      </c>
+      <c r="K18" t="s">
+        <v>178</v>
+      </c>
+      <c r="L18" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" t="s">
+        <v>157</v>
+      </c>
+      <c r="N18" t="s">
+        <v>152</v>
+      </c>
+      <c r="O18" t="s">
         <v>169</v>
       </c>
-      <c r="K18" t="s">
-        <v>170</v>
-      </c>
-      <c r="L18" t="s">
-        <v>144</v>
-      </c>
-      <c r="M18" t="s">
-        <v>151</v>
-      </c>
-      <c r="N18" t="s">
-        <v>146</v>
-      </c>
-      <c r="O18" t="s">
-        <v>162</v>
-      </c>
       <c r="P18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T18" t="s">
         <v>9</v>
       </c>
       <c r="U18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA18" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="AB18" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AC18" t="s">
-        <v>153</v>
+        <v>180</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="19">
       <c r="J19" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M19" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O19" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="P19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T19" t="s">
         <v>9</v>
       </c>
       <c r="U19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y19" t="s">
         <v>10</v>
       </c>
       <c r="Z19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA19" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AB19" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="AC19" t="s">
-        <v>153</v>
+        <v>97</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="J20" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="K20" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O20" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="P20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T20" t="s">
         <v>9</v>
       </c>
       <c r="U20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y20" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Z20" t="s">
         <v>10</v>
       </c>
       <c r="AA20" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AB20" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="AC20" t="s">
-        <v>153</v>
+        <v>159</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J21" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="K21" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O21" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="P21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T21" t="s">
         <v>9</v>
       </c>
       <c r="U21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA21" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="AB21" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="AC21" t="s">
-        <v>153</v>
+        <v>165</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="22">
@@ -2252,10 +2342,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="D22" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="E22" t="s">
         <v>4</v>
@@ -2264,661 +2354,688 @@
         <v>5</v>
       </c>
       <c r="J22" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="K22" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N22" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O22" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="P22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T22" t="s">
         <v>9</v>
       </c>
       <c r="U22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z22" t="s">
         <v>10</v>
       </c>
       <c r="AA22" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="AB22" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="AC22" t="s">
-        <v>153</v>
+        <v>172</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="J23" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K23" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L23" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N23" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O23" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="P23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T23" t="s">
         <v>9</v>
       </c>
       <c r="U23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y23" t="s">
         <v>10</v>
       </c>
       <c r="Z23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA23" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="AB23" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="AC23" t="s">
-        <v>158</v>
+        <v>176</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D24" t="s">
         <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
         <v>31</v>
       </c>
       <c r="J24" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L24" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M24" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N24" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O24" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="P24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T24" t="s">
         <v>9</v>
       </c>
       <c r="U24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA24" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="AB24" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="AC24" t="s">
-        <v>158</v>
+        <v>180</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="D25" t="s">
         <v>33</v>
       </c>
       <c r="E25" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
       </c>
       <c r="J25" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="K25" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M25" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N25" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O25" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="P25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T25" t="s">
         <v>9</v>
       </c>
       <c r="U25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y25" t="s">
         <v>10</v>
       </c>
       <c r="Z25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA25" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AB25" t="s">
-        <v>94</v>
+        <v>208</v>
       </c>
       <c r="AC25" t="s">
-        <v>158</v>
+        <v>97</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
       </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F26" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="J26" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K26" t="s">
+        <v>210</v>
+      </c>
+      <c r="L26" t="s">
         <v>199</v>
       </c>
-      <c r="L26" t="s">
-        <v>189</v>
-      </c>
       <c r="M26" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N26" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O26" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T26" t="s">
         <v>9</v>
       </c>
       <c r="U26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z26" t="s">
         <v>10</v>
       </c>
       <c r="AA26" t="s">
-        <v>200</v>
+        <v>86</v>
       </c>
       <c r="AB26" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="AC26" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="J27" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="K27" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="L27" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M27" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N27" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O27" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="P27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T27" t="s">
         <v>9</v>
       </c>
       <c r="U27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z27" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA27" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="AB27" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="AC27" t="s">
-        <v>158</v>
+        <v>165</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D28" t="s">
         <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="J28" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="K28" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="L28" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M28" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N28" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O28" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="P28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z28" t="s">
         <v>10</v>
       </c>
       <c r="AA28" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="AB28" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="AC28" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="J29" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K29" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="L29" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N29" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O29" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="P29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q29" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T29" t="s">
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y29" t="s">
         <v>10</v>
       </c>
       <c r="Z29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA29" t="s">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AB29" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="AC29" t="s">
-        <v>164</v>
+        <v>176</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="J30" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="K30" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="L30" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N30" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O30" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="P30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T30" t="s">
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z30" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA30" t="s">
-        <v>214</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>180</v>
+      </c>
+      <c r="AD30" t="s">
         <v>172</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D31" t="s">
         <v>52</v>
@@ -2927,769 +3044,805 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="J31" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="K31" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="L31" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M31" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N31" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O31" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S31" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T31" t="s">
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y31" t="s">
         <v>10</v>
       </c>
       <c r="Z31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA31" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="AB31" t="s">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="AC31" t="s">
-        <v>164</v>
+        <v>97</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D32" t="s">
         <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="J32" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="K32" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="L32" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M32" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N32" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O32" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S32" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T32" t="s">
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z32" t="s">
         <v>10</v>
       </c>
       <c r="AA32" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="AB32" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="AC32" t="s">
-        <v>164</v>
+        <v>159</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="33">
       <c r="J33" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="K33" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="L33" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M33" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N33" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O33" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S33" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T33" t="s">
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y33" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z33" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA33" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="AB33" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AC33" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="34">
       <c r="J34" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="K34" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="L34" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N34" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O34" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q34" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R34" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S34" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T34" t="s">
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z34" t="s">
         <v>10</v>
       </c>
       <c r="AA34" t="s">
-        <v>229</v>
+        <v>10</v>
       </c>
       <c r="AB34" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="AC34" t="s">
-        <v>168</v>
+        <v>172</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="35">
       <c r="J35" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="K35" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L35" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M35" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N35" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O35" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="P35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T35" t="s">
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y35" t="s">
         <v>10</v>
       </c>
       <c r="Z35" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA35" t="s">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="AB35" t="s">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="AC35" t="s">
-        <v>168</v>
+        <v>176</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="36">
       <c r="J36" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="K36" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="L36" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M36" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N36" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O36" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="P36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q36" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R36" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S36" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T36" t="s">
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y36" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z36" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA36" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="AB36" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="AC36" t="s">
-        <v>168</v>
+        <v>180</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="37">
       <c r="J37" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="K37" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="L37" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N37" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O37" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="P37" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R37" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S37" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T37" t="s">
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s">
         <v>10</v>
       </c>
       <c r="Z37" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA37" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="AB37" t="s">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="AC37" t="s">
-        <v>168</v>
+        <v>97</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="J38" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="K38" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="L38" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N38" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O38" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="P38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R38" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S38" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T38" t="s">
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y38" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z38" t="s">
         <v>10</v>
       </c>
       <c r="AA38" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="AB38" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="AC38" t="s">
-        <v>172</v>
+        <v>159</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="39">
       <c r="J39" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="K39" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="L39" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M39" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="N39" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O39" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="P39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q39" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S39" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T39" t="s">
         <v>12</v>
       </c>
       <c r="U39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA39" t="s">
-        <v>245</v>
+        <v>163</v>
       </c>
       <c r="AB39" t="s">
-        <v>158</v>
+        <v>256</v>
       </c>
       <c r="AC39" t="s">
-        <v>172</v>
+        <v>165</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="J40" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="K40" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="L40" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M40" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N40" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O40" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="P40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q40" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R40" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S40" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T40" t="s">
         <v>12</v>
       </c>
       <c r="U40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z40" t="s">
         <v>10</v>
       </c>
       <c r="AA40" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="AB40" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="AC40" t="s">
         <v>172</v>
       </c>
+      <c r="AD40" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="41">
       <c r="J41" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="K41" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="L41" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M41" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N41" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O41" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="P41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q41" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R41" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S41" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T41" t="s">
         <v>12</v>
       </c>
       <c r="U41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s">
         <v>10</v>
       </c>
       <c r="Z41" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA41" t="s">
-        <v>252</v>
+        <v>81</v>
       </c>
       <c r="AB41" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="AC41" t="s">
-        <v>172</v>
+        <v>176</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="42">
       <c r="J42" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="K42" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="L42" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M42" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N42" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O42" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="P42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q42" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R42" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S42" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T42" t="s">
         <v>12</v>
       </c>
       <c r="U42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z42" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AA42" t="s">
-        <v>255</v>
+        <v>10</v>
       </c>
       <c r="AB42" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="AC42" t="s">
-        <v>172</v>
+        <v>180</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="47">
       <c r="I47" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48">
@@ -3700,10 +3853,10 @@
         <v>23</v>
       </c>
       <c r="K48" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="L48" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49">
@@ -3728,10 +3881,10 @@
         <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="L50" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51">
@@ -3753,175 +3906,175 @@
         <v>10</v>
       </c>
       <c r="K52" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="L52" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53">
       <c r="J53" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K53" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="L53" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54">
       <c r="J54" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K54" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="L54" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55">
       <c r="J55" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K55" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="L55" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56">
       <c r="J56" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K56" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="L56" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57">
       <c r="J57" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K57" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L57" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58">
       <c r="J58" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K58" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="L58" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59">
       <c r="J59" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K59" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="L59" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60">
       <c r="J60" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K60" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L60" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61">
       <c r="J61" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K61" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="L61" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62">
       <c r="J62" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K62" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="L62" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63">
       <c r="J63" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="K63" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="L63" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64">
       <c r="J64" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="K64" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="L64" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65">
       <c r="J65" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="K65" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="L65" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66">
       <c r="J66" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="K66" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="L66" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67">
       <c r="J67" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K67" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="L67" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/xlsx/conformance/conformance.xlsx
+++ b/test/fixtures/xlsx/conformance/conformance.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="343">
   <si>
     <t xml:space="preserve">:enum Flag</t>
   </si>
@@ -975,6 +975,72 @@
   </si>
   <si>
     <t xml:space="preserve">names the reader's uuid type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha;é한Ａ;gamma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text elements, beyond ascii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigint[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9223372036854775807;-9223372036854775807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elements past what a double carries exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5;0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single precision elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y;N;Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logical elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One;Large;Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enum elements, which name the enum</t>
   </si>
 </sst>
 </file>
@@ -3188,6 +3254,18 @@
       </c>
     </row>
     <row r="33">
+      <c r="C33" t="s">
+        <v>321</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F33" t="s">
+        <v>323</v>
+      </c>
       <c r="J33" t="s">
         <v>233</v>
       </c>
@@ -3253,6 +3331,18 @@
       </c>
     </row>
     <row r="34">
+      <c r="C34" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" t="s">
+        <v>325</v>
+      </c>
       <c r="J34" t="s">
         <v>237</v>
       </c>
@@ -3318,6 +3408,18 @@
       </c>
     </row>
     <row r="35">
+      <c r="C35" t="s">
+        <v>326</v>
+      </c>
+      <c r="D35" t="s">
+        <v>327</v>
+      </c>
+      <c r="E35" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" t="s">
+        <v>329</v>
+      </c>
       <c r="J35" t="s">
         <v>241</v>
       </c>
@@ -3383,6 +3485,18 @@
       </c>
     </row>
     <row r="36">
+      <c r="C36" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" t="s">
+        <v>331</v>
+      </c>
+      <c r="E36" t="s">
+        <v>332</v>
+      </c>
+      <c r="F36" t="s">
+        <v>333</v>
+      </c>
       <c r="J36" t="s">
         <v>244</v>
       </c>
@@ -3448,6 +3562,18 @@
       </c>
     </row>
     <row r="37">
+      <c r="C37" t="s">
+        <v>334</v>
+      </c>
+      <c r="D37" t="s">
+        <v>335</v>
+      </c>
+      <c r="E37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" t="s">
+        <v>337</v>
+      </c>
       <c r="J37" t="s">
         <v>247</v>
       </c>
@@ -3513,6 +3639,18 @@
       </c>
     </row>
     <row r="38">
+      <c r="C38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" t="s">
+        <v>339</v>
+      </c>
       <c r="J38" t="s">
         <v>251</v>
       </c>
@@ -3578,6 +3716,18 @@
       </c>
     </row>
     <row r="39">
+      <c r="C39" t="s">
+        <v>340</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>341</v>
+      </c>
+      <c r="F39" t="s">
+        <v>342</v>
+      </c>
       <c r="J39" t="s">
         <v>254</v>
       </c>
